--- a/registration_forms/029_lean_six_sigma_certification_exam_form--registration_forms.xlsx
+++ b/registration_forms/029_lean_six_sigma_certification_exam_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submission_status</t>
+          <t>submission_status_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submission Status</t>
+          <t>Submission Status 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>agreement_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Agreement</t>
+          <t>Agreement 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>agreement_date</t>
+          <t>agreement_date_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agreement Date</t>
+          <t>Agreement Date 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>agreement_time</t>
+          <t>agreement_time_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Agreement Time</t>
+          <t>Agreement Time 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1006,12 +1006,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1124,63 +1124,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_status_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_status_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_status_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -1209,80 +1209,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>agreement_choices</t>
+          <t>agreement_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>agreement_choices</t>
+          <t>agreement_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>agreement_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>agreement_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
